--- a/database/event/5715/event_5715_evp_summary.xlsx
+++ b/database/event/5715/event_5715_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3334</v>
+        <v>5.1916</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3811</v>
+        <v>1.3444</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7332</v>
+        <v>1.6244</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3334</v>
+        <v>5.1916</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3334</v>
+        <v>5.1916</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0596</v>
+        <v>5.8373</v>
       </c>
       <c r="I2" t="n">
         <v>6.3476</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7849</v>
+        <v>4.6872</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2391</v>
+        <v>1.2138</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5116</v>
+        <v>1.4235</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7849</v>
+        <v>4.6872</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7849</v>
+        <v>4.6872</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1997</v>
+        <v>5.0465</v>
       </c>
       <c r="I3" t="n">
         <v>5.3965</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.652</v>
+        <v>4.5352</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2047</v>
+        <v>1.1744</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4579</v>
+        <v>1.3629</v>
       </c>
       <c r="E4" t="n">
-        <v>4.652</v>
+        <v>4.5352</v>
       </c>
       <c r="F4" t="n">
-        <v>4.652</v>
+        <v>4.5352</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9912</v>
+        <v>4.8081</v>
       </c>
       <c r="I4" t="n">
         <v>5.2285</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1803</v>
+        <v>4.1004</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0825</v>
+        <v>1.0618</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2674</v>
+        <v>1.1897</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1803</v>
+        <v>4.1004</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1803</v>
+        <v>4.1004</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2516</v>
+        <v>4.1264</v>
       </c>
       <c r="I5" t="n">
         <v>4.4125</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0779</v>
+        <v>4.0004</v>
       </c>
       <c r="C6" t="n">
-        <v>1.056</v>
+        <v>1.0359</v>
       </c>
       <c r="D6" t="n">
-        <v>1.226</v>
+        <v>1.1498</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0779</v>
+        <v>4.0004</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0779</v>
+        <v>4.0004</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0911</v>
+        <v>4.0004</v>
       </c>
       <c r="I6" t="n">
         <v>4.2067</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8732</v>
+        <v>3.7311</v>
       </c>
       <c r="C7" t="n">
-        <v>1.003</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1433</v>
+        <v>1.0426</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8732</v>
+        <v>3.7311</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8732</v>
+        <v>3.7311</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8732</v>
+        <v>3.7311</v>
       </c>
       <c r="I7" t="n">
         <v>4.0573</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5587</v>
+        <v>3.4928</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9215</v>
+        <v>0.9045</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0163</v>
+        <v>0.9476</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5587</v>
+        <v>3.4928</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5587</v>
+        <v>3.4928</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5587</v>
+        <v>3.4928</v>
       </c>
       <c r="I8" t="n">
         <v>3.6423</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0993</v>
+        <v>3.0533</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8026</v>
+        <v>0.7907</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8307</v>
+        <v>0.7725</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0993</v>
+        <v>3.0533</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0993</v>
+        <v>3.0533</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0993</v>
+        <v>3.0533</v>
       </c>
       <c r="I9" t="n">
         <v>3.1574</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0982</v>
+        <v>3.0076</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8023</v>
+        <v>0.7788</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8302</v>
+        <v>0.7543</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0982</v>
+        <v>3.0076</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0982</v>
+        <v>3.0076</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0982</v>
+        <v>3.0076</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2455</v>
+        <v>3.1894</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2455</v>
+        <v>3.1894</v>
       </c>
       <c r="N10" t="n">
-        <v>255</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0874</v>
+        <v>2.9846</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7995</v>
+        <v>0.7729</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8259</v>
+        <v>0.7452</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0874</v>
+        <v>2.9846</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0874</v>
+        <v>2.9846</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0874</v>
+        <v>2.9846</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1894</v>
+        <v>3.2455</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>255</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1894</v>
+        <v>3.2455</v>
       </c>
       <c r="N11" t="n">
-        <v>394</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.779</v>
+        <v>2.7174</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7196</v>
+        <v>0.7037</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7013</v>
+        <v>0.6387</v>
       </c>
       <c r="E12" t="n">
-        <v>2.779</v>
+        <v>2.7174</v>
       </c>
       <c r="F12" t="n">
-        <v>2.779</v>
+        <v>2.7174</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.779</v>
+        <v>2.7174</v>
       </c>
       <c r="I12" t="n">
         <v>2.8575</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3492</v>
+        <v>2.323</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6083</v>
+        <v>0.6016</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.4816</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3492</v>
+        <v>2.323</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3492</v>
+        <v>2.323</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3492</v>
+        <v>2.323</v>
       </c>
       <c r="I13" t="n">
         <v>2.3821</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.294</v>
+        <v>2.2431</v>
       </c>
       <c r="C14" t="n">
-        <v>0.594</v>
+        <v>0.5809</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5054</v>
+        <v>0.4497</v>
       </c>
       <c r="E14" t="n">
-        <v>2.294</v>
+        <v>2.2431</v>
       </c>
       <c r="F14" t="n">
-        <v>2.294</v>
+        <v>2.2431</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.294</v>
+        <v>2.2431</v>
       </c>
       <c r="I14" t="n">
         <v>2.3588</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>HEAP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.232</v>
+        <v>2.1878</v>
       </c>
       <c r="C15" t="n">
-        <v>0.578</v>
+        <v>0.5665</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4803</v>
+        <v>0.4277</v>
       </c>
       <c r="E15" t="n">
-        <v>2.232</v>
+        <v>2.1878</v>
       </c>
       <c r="F15" t="n">
-        <v>2.232</v>
+        <v>2.1878</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.232</v>
+        <v>2.1878</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3057</v>
+        <v>2.2814</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>394</v>
+        <v>301</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3057</v>
+        <v>2.2814</v>
       </c>
       <c r="N15" t="n">
-        <v>394</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HEAP</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.229</v>
+        <v>2.1743</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5772</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4791</v>
+        <v>0.4223</v>
       </c>
       <c r="E16" t="n">
-        <v>2.229</v>
+        <v>2.1743</v>
       </c>
       <c r="F16" t="n">
-        <v>2.229</v>
+        <v>2.1743</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.229</v>
+        <v>2.1743</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2814</v>
+        <v>2.3057</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2814</v>
+        <v>2.3057</v>
       </c>
       <c r="N16" t="n">
-        <v>301</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1472</v>
+        <v>2.0995</v>
       </c>
       <c r="C17" t="n">
-        <v>0.556</v>
+        <v>0.5437</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4461</v>
+        <v>0.3925</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1472</v>
+        <v>2.0995</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1472</v>
+        <v>2.0995</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1472</v>
+        <v>2.0995</v>
       </c>
       <c r="I17" t="n">
         <v>2.2078</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1109</v>
+        <v>2.0563</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5466</v>
+        <v>0.5325</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4314</v>
+        <v>0.3753</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1109</v>
+        <v>2.0563</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1109</v>
+        <v>2.0563</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1109</v>
+        <v>2.0563</v>
       </c>
       <c r="I18" t="n">
         <v>2.1806</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.075</v>
+        <v>2.029</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5373</v>
+        <v>0.5254</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4169</v>
+        <v>0.3644</v>
       </c>
       <c r="E19" t="n">
-        <v>2.075</v>
+        <v>2.029</v>
       </c>
       <c r="F19" t="n">
-        <v>2.075</v>
+        <v>2.029</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.075</v>
+        <v>2.029</v>
       </c>
       <c r="I19" t="n">
         <v>2.1336</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0435</v>
+        <v>2.0057</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5292</v>
+        <v>0.5194</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4042</v>
+        <v>0.3552</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0435</v>
+        <v>2.0057</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0435</v>
+        <v>2.0057</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0435</v>
+        <v>2.0057</v>
       </c>
       <c r="I20" t="n">
         <v>2.0915</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.824</v>
+        <v>1.7669</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4723</v>
+        <v>0.4575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3155</v>
+        <v>0.26</v>
       </c>
       <c r="E21" t="n">
-        <v>1.824</v>
+        <v>1.7669</v>
       </c>
       <c r="F21" t="n">
-        <v>1.824</v>
+        <v>1.7669</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.824</v>
+        <v>1.7669</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9107</v>
+        <v>1.8271</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9107</v>
+        <v>1.8271</v>
       </c>
       <c r="N21" t="n">
-        <v>255</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7935</v>
+        <v>1.7571</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4644</v>
+        <v>0.455</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3032</v>
+        <v>0.2561</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7935</v>
+        <v>1.7571</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7935</v>
+        <v>1.7571</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7935</v>
+        <v>1.7571</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8271</v>
+        <v>1.9107</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>319</v>
+        <v>255</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8271</v>
+        <v>1.9107</v>
       </c>
       <c r="N22" t="n">
-        <v>319</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23">
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7793</v>
+        <v>1.7529</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4608</v>
+        <v>0.4539</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2974</v>
+        <v>0.2544</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7793</v>
+        <v>1.7529</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7793</v>
+        <v>1.7529</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7793</v>
+        <v>1.7529</v>
       </c>
       <c r="I23" t="n">
         <v>1.8127</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6793</v>
+        <v>1.6421</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4349</v>
+        <v>0.4252</v>
       </c>
       <c r="D24" t="n">
-        <v>0.257</v>
+        <v>0.2103</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6793</v>
+        <v>1.6421</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6793</v>
+        <v>1.6421</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6793</v>
+        <v>1.6421</v>
       </c>
       <c r="I24" t="n">
         <v>1.7268</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4879</v>
+        <v>1.4603</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3853</v>
+        <v>0.3782</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1797</v>
+        <v>0.1379</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4879</v>
+        <v>1.4603</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4879</v>
+        <v>1.4603</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4879</v>
+        <v>1.4603</v>
       </c>
       <c r="I25" t="n">
         <v>1.5228</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4623</v>
+        <v>1.4245</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3787</v>
+        <v>0.3689</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1694</v>
+        <v>0.1236</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4623</v>
+        <v>1.4245</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4623</v>
+        <v>1.4245</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4623</v>
+        <v>1.4245</v>
       </c>
       <c r="I26" t="n">
         <v>1.5106</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3545</v>
+        <v>1.3278</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3508</v>
+        <v>0.3438</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1258</v>
+        <v>0.0851</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3545</v>
+        <v>1.3278</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3545</v>
+        <v>1.3278</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3545</v>
+        <v>1.3278</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3927</v>
+        <v>1.3846</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3927</v>
+        <v>1.3846</v>
       </c>
       <c r="N27" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3528</v>
+        <v>1.3271</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3503</v>
+        <v>0.3437</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1251</v>
+        <v>0.0848</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3528</v>
+        <v>1.3271</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3528</v>
+        <v>1.3271</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3528</v>
+        <v>1.3271</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3846</v>
+        <v>1.3609</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3846</v>
+        <v>1.3609</v>
       </c>
       <c r="N28" t="n">
-        <v>311</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3421</v>
+        <v>1.3244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3475</v>
+        <v>0.343</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1208</v>
+        <v>0.0837</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3421</v>
+        <v>1.3244</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3421</v>
+        <v>1.3244</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3421</v>
+        <v>1.3244</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3609</v>
+        <v>1.3927</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3609</v>
+        <v>1.3927</v>
       </c>
       <c r="N29" t="n">
-        <v>251</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30">
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3369</v>
+        <v>1.2975</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3462</v>
+        <v>0.336</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1187</v>
+        <v>0.073</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3369</v>
+        <v>1.2975</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3369</v>
+        <v>1.2975</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3369</v>
+        <v>1.2975</v>
       </c>
       <c r="I30" t="n">
         <v>1.3875</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9655</v>
+        <v>0.9537</v>
       </c>
       <c r="C31" t="n">
-        <v>0.25</v>
+        <v>0.247</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0313</v>
+        <v>-0.064</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9655</v>
+        <v>0.9537</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9655</v>
+        <v>0.9537</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9655</v>
+        <v>0.9537</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9836</v>
+        <v>0.978</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9836</v>
+        <v>0.978</v>
       </c>
       <c r="N31" t="n">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9645</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2498</v>
+        <v>0.2463</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0317</v>
+        <v>-0.065</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9645</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9645</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9645</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.978</v>
+        <v>0.9836</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.978</v>
+        <v>0.9836</v>
       </c>
       <c r="N32" t="n">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33">
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8892</v>
+        <v>0.876</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2303</v>
+        <v>0.2268</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0621</v>
+        <v>-0.0949</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8892</v>
+        <v>0.876</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8892</v>
+        <v>0.876</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8892</v>
+        <v>0.876</v>
       </c>
       <c r="I33" t="n">
         <v>0.9059</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8627</v>
+        <v>0.8499</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2234</v>
+        <v>0.2201</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1053</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8627</v>
+        <v>0.8499</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8627</v>
+        <v>0.8499</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8627</v>
+        <v>0.8499</v>
       </c>
       <c r="I34" t="n">
         <v>0.8789</v>
@@ -2020,7 +2020,7 @@
         <v>0.1736</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1506</v>
+        <v>-0.1769</v>
       </c>
       <c r="E35" t="n">
         <v>0.6703</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6069</v>
+        <v>0.6001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1572</v>
+        <v>0.1554</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1762</v>
+        <v>-0.2048</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6069</v>
+        <v>0.6001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6069</v>
+        <v>0.6001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6069</v>
+        <v>0.6001</v>
       </c>
       <c r="I36" t="n">
         <v>0.6153999999999999</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5906</v>
+        <v>0.5797</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1529</v>
+        <v>0.1501</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1828</v>
+        <v>-0.213</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5906</v>
+        <v>0.5797</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5906</v>
+        <v>0.5797</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5906</v>
+        <v>0.5797</v>
       </c>
       <c r="I37" t="n">
         <v>0.6045</v>
@@ -2158,7 +2158,7 @@
         <v>0.1407</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2019</v>
+        <v>-0.2275</v>
       </c>
       <c r="E38" t="n">
         <v>0.5432</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.239</v>
+        <v>0.2337</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0619</v>
+        <v>0.0605</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3248</v>
+        <v>-0.3508</v>
       </c>
       <c r="E39" t="n">
-        <v>0.239</v>
+        <v>0.2337</v>
       </c>
       <c r="F39" t="n">
-        <v>0.239</v>
+        <v>0.2337</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.239</v>
+        <v>0.2337</v>
       </c>
       <c r="I39" t="n">
         <v>0.2458</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1062</v>
+        <v>0.1058</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0275</v>
+        <v>0.0274</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3785</v>
+        <v>-0.4018</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1062</v>
+        <v>0.1058</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1062</v>
+        <v>0.1058</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1062</v>
+        <v>0.1058</v>
       </c>
       <c r="I40" t="n">
         <v>0.1067</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0747</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0193</v>
+        <v>-0.019</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4515</v>
+        <v>-0.4732</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0747</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0747</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0747</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>-0.0765</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1905</v>
+        <v>-0.1863</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0493</v>
+        <v>-0.0482</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4983</v>
+        <v>-0.5181</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1905</v>
+        <v>-0.1863</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1905</v>
+        <v>-0.1863</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1905</v>
+        <v>-0.1863</v>
       </c>
       <c r="I42" t="n">
         <v>-0.1959</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2138</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0564</v>
+        <v>-0.0554</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5093</v>
+        <v>-0.5291</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2138</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2138</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2178</v>
+        <v>-0.2138</v>
       </c>
       <c r="I43" t="n">
         <v>-0.2229</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3677</v>
+        <v>-0.3663</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0949</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5699</v>
+        <v>-0.5898</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.3677</v>
+        <v>-0.3663</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3677</v>
+        <v>-0.3663</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3677</v>
+        <v>-0.3663</v>
       </c>
       <c r="I44" t="n">
         <v>-0.3694</v>
@@ -2480,7 +2480,7 @@
         <v>-0.111</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5946</v>
+        <v>-0.6147</v>
       </c>
       <c r="E45" t="n">
         <v>-0.4288</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1237</v>
+        <v>-0.1232</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6143</v>
+        <v>-0.6334</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="I46" t="n">
         <v>-0.4797</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5991</v>
+        <v>-0.588</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1551</v>
+        <v>-0.1523</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6634</v>
+        <v>-0.6782</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5991</v>
+        <v>-0.588</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.5991</v>
+        <v>-0.588</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5991</v>
+        <v>-0.588</v>
       </c>
       <c r="I47" t="n">
         <v>-0.6132</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6701</v>
+        <v>-0.6602</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1735</v>
+        <v>-0.171</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6921</v>
+        <v>-0.7069</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6701</v>
+        <v>-0.6602</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6701</v>
+        <v>-0.6602</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6701</v>
+        <v>-0.6602</v>
       </c>
       <c r="I48" t="n">
         <v>-0.6827</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.7313</v>
+        <v>-0.7178</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1894</v>
+        <v>-0.1859</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7168</v>
+        <v>-0.7299</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.7313</v>
+        <v>-0.7178</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.7313</v>
+        <v>-0.7178</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7313</v>
+        <v>-0.7178</v>
       </c>
       <c r="I49" t="n">
         <v>-0.7485000000000001</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7362</v>
+        <v>-0.7199</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1906</v>
+        <v>-0.1864</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7188</v>
+        <v>-0.7307</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7362</v>
+        <v>-0.7199</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7362</v>
+        <v>-0.7199</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7362</v>
+        <v>-0.7199</v>
       </c>
       <c r="I50" t="n">
         <v>-0.757</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8784</v>
+        <v>-0.8686</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2275</v>
+        <v>-0.2249</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7762</v>
+        <v>-0.79</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.8784</v>
+        <v>-0.8686</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.8784</v>
+        <v>-0.8686</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8784</v>
+        <v>-0.8686</v>
       </c>
       <c r="I51" t="n">
         <v>-0.8908</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9405</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2435</v>
+        <v>-0.2426</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8013</v>
+        <v>-0.8172</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.9405</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.9405</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.9405</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>-0.9449</v>
@@ -2838,93 +2838,93 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.0072</v>
+        <v>-0.9827</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2608</v>
+        <v>-0.2545</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8282</v>
+        <v>-0.8354</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.0072</v>
+        <v>-0.9827</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.0072</v>
+        <v>-0.9827</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.0072</v>
+        <v>-0.9827</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0261</v>
+        <v>-1.0508</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.0261</v>
+        <v>-1.0508</v>
       </c>
       <c r="N53" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0125</v>
+        <v>-0.9923</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2622</v>
+        <v>-0.257</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8304</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.0125</v>
+        <v>-0.9923</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.0125</v>
+        <v>-0.9923</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.0125</v>
+        <v>-0.9923</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0508</v>
+        <v>-1.0261</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.0508</v>
+        <v>-1.0261</v>
       </c>
       <c r="N54" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55">
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.0318</v>
+        <v>-1.0052</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2672</v>
+        <v>-0.2603</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.8444</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.0318</v>
+        <v>-1.0052</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.0318</v>
+        <v>-1.0052</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.0318</v>
+        <v>-1.0052</v>
       </c>
       <c r="I55" t="n">
         <v>-1.0659</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2691</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.858</v>
       </c>
       <c r="E56" t="n">
         <v>-1.0393</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.1847</v>
+        <v>-1.1803</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3068</v>
+        <v>-0.3056</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9</v>
+        <v>-0.9141</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.1847</v>
+        <v>-1.1803</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.1847</v>
+        <v>-1.1803</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.1847</v>
+        <v>-1.1803</v>
       </c>
       <c r="I57" t="n">
         <v>-1.1902</v>
@@ -3078,7 +3078,7 @@
         <v>-0.4273</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0879</v>
+        <v>-1.1013</v>
       </c>
       <c r="E58" t="n">
         <v>-1.65</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.4209</v>
+        <v>-2.385</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6269</v>
+        <v>-0.6176</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.3994</v>
+        <v>-1.3941</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.4209</v>
+        <v>-2.385</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.4209</v>
+        <v>-2.385</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.4209</v>
+        <v>-2.385</v>
       </c>
       <c r="I59" t="n">
         <v>-2.4663</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.6479</v>
+        <v>-2.5699</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.6857</v>
+        <v>-0.6655</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4911</v>
+        <v>-1.4678</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.6479</v>
+        <v>-2.5699</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.6479</v>
+        <v>-2.5699</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.6479</v>
+        <v>-2.5699</v>
       </c>
       <c r="I60" t="n">
         <v>-2.7481</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.7047</v>
+        <v>-2.6646</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.7004</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.514</v>
+        <v>-1.5055</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.7047</v>
+        <v>-2.6646</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.7047</v>
+        <v>-2.6646</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.7047</v>
+        <v>-2.6646</v>
       </c>
       <c r="I61" t="n">
         <v>-2.7554</v>
